--- a/Team-Data/2012-13/1-25-2012-13.xlsx
+++ b/Team-Data/2012-13/1-25-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,25 +728,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
         <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>0.581</v>
+        <v>0.571</v>
       </c>
       <c r="H2" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J2" t="n">
-        <v>81.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>0.457</v>
@@ -688,34 +755,34 @@
         <v>8.800000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.38</v>
+        <v>0.382</v>
       </c>
       <c r="O2" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="P2" t="n">
-        <v>19.1</v>
+        <v>18.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.698</v>
+        <v>0.696</v>
       </c>
       <c r="R2" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>30.9</v>
+        <v>30.7</v>
       </c>
       <c r="T2" t="n">
-        <v>40.7</v>
+        <v>40.5</v>
       </c>
       <c r="U2" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="V2" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W2" t="n">
         <v>8.300000000000001</v>
@@ -724,22 +791,22 @@
         <v>4.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>96.59999999999999</v>
+        <v>96</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -751,25 +818,25 @@
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AI2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
         <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO2" t="n">
         <v>28</v>
@@ -778,16 +845,16 @@
         <v>27</v>
       </c>
       <c r="AQ2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR2" t="n">
         <v>26</v>
       </c>
       <c r="AS2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
@@ -796,13 +863,13 @@
         <v>22</v>
       </c>
       <c r="AW2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY2" t="n">
         <v>11</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>10</v>
       </c>
       <c r="AZ2" t="n">
         <v>3</v>
@@ -811,7 +878,7 @@
         <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -843,28 +910,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" t="n">
-        <v>0.465</v>
+        <v>0.476</v>
       </c>
       <c r="H3" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="I3" t="n">
-        <v>36.7</v>
+        <v>36.5</v>
       </c>
       <c r="J3" t="n">
-        <v>80.2</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L3" t="n">
         <v>5.4</v>
@@ -873,70 +940,70 @@
         <v>16.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.335</v>
+        <v>0.334</v>
       </c>
       <c r="O3" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P3" t="n">
         <v>20.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.78</v>
+        <v>0.775</v>
       </c>
       <c r="R3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="S3" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="T3" t="n">
-        <v>39.5</v>
+        <v>39.3</v>
       </c>
       <c r="U3" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V3" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="W3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>95</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.4</v>
+        <v>-1.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
         <v>17</v>
       </c>
       <c r="AF3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG3" t="n">
         <v>17</v>
       </c>
       <c r="AH3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AJ3" t="n">
         <v>27</v>
@@ -945,7 +1012,7 @@
         <v>6</v>
       </c>
       <c r="AL3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM3" t="n">
         <v>28</v>
@@ -954,10 +1021,10 @@
         <v>27</v>
       </c>
       <c r="AO3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ3" t="n">
         <v>8</v>
@@ -966,34 +1033,34 @@
         <v>28</v>
       </c>
       <c r="AS3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AW3" t="n">
         <v>3</v>
       </c>
       <c r="AX3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA3" t="n">
         <v>14</v>
       </c>
       <c r="BB3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC3" t="n">
         <v>18</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -1025,37 +1092,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E4" t="n">
         <v>26</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>0.605</v>
+        <v>0.619</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="J4" t="n">
-        <v>79.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K4" t="n">
         <v>0.442</v>
       </c>
       <c r="L4" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M4" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0.343</v>
+        <v>0.346</v>
       </c>
       <c r="O4" t="n">
         <v>18.3</v>
@@ -1064,22 +1131,22 @@
         <v>24.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.747</v>
+        <v>0.75</v>
       </c>
       <c r="R4" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S4" t="n">
         <v>29.6</v>
       </c>
       <c r="T4" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U4" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W4" t="n">
         <v>7.2</v>
@@ -1091,40 +1158,40 @@
         <v>4.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="AA4" t="n">
         <v>21.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.8</v>
+        <v>96.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
         <v>6</v>
       </c>
       <c r="AF4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ4" t="n">
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
         <v>11</v>
@@ -1133,7 +1200,7 @@
         <v>9</v>
       </c>
       <c r="AN4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="n">
         <v>7</v>
@@ -1142,7 +1209,7 @@
         <v>7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR4" t="n">
         <v>7</v>
@@ -1151,7 +1218,7 @@
         <v>24</v>
       </c>
       <c r="AT4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU4" t="n">
         <v>25</v>
@@ -1163,7 +1230,7 @@
         <v>25</v>
       </c>
       <c r="AX4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY4" t="n">
         <v>6</v>
@@ -1175,10 +1242,10 @@
         <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>29</v>
@@ -1294,13 +1361,13 @@
         <v>29</v>
       </c>
       <c r="AG5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ5" t="n">
         <v>16</v>
@@ -1324,7 +1391,7 @@
         <v>3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR5" t="n">
         <v>14</v>
@@ -1357,7 +1424,7 @@
         <v>4</v>
       </c>
       <c r="BB5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -1389,55 +1456,55 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
         <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>0.619</v>
+        <v>0.61</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
       </c>
       <c r="I6" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J6" t="n">
-        <v>81</v>
+        <v>80.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="M6" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.359</v>
+        <v>0.356</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="P6" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.78</v>
+        <v>0.783</v>
       </c>
       <c r="R6" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S6" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="T6" t="n">
-        <v>44</v>
+        <v>43.7</v>
       </c>
       <c r="U6" t="n">
         <v>22.8</v>
@@ -1446,58 +1513,58 @@
         <v>14.9</v>
       </c>
       <c r="W6" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y6" t="n">
         <v>5.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA6" t="n">
         <v>20.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AF6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI6" t="n">
         <v>25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
         <v>22</v>
       </c>
       <c r="AL6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM6" t="n">
         <v>30</v>
       </c>
       <c r="AN6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
         <v>8</v>
@@ -1509,40 +1576,40 @@
         <v>7</v>
       </c>
       <c r="AR6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
         <v>11</v>
       </c>
       <c r="AT6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW6" t="n">
         <v>24</v>
       </c>
       <c r="AX6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AY6" t="n">
         <v>21</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB6" t="n">
         <v>25</v>
       </c>
       <c r="BC6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -1571,37 +1638,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
         <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>0.273</v>
+        <v>0.256</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>35.7</v>
+        <v>35.5</v>
       </c>
       <c r="J7" t="n">
-        <v>84.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.422</v>
+        <v>0.42</v>
       </c>
       <c r="L7" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M7" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="O7" t="n">
         <v>16.7</v>
@@ -1613,16 +1680,16 @@
         <v>0.75</v>
       </c>
       <c r="R7" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S7" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="T7" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="U7" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="V7" t="n">
         <v>14.7</v>
@@ -1637,19 +1704,19 @@
         <v>7</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
         <v>20.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>95.5</v>
+        <v>95</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.1</v>
+        <v>-5.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
@@ -1670,7 +1737,7 @@
         <v>3</v>
       </c>
       <c r="AK7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL7" t="n">
         <v>12</v>
@@ -1679,7 +1746,7 @@
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
         <v>16</v>
@@ -1691,7 +1758,7 @@
         <v>17</v>
       </c>
       <c r="AR7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS7" t="n">
         <v>30</v>
@@ -1700,7 +1767,7 @@
         <v>21</v>
       </c>
       <c r="AU7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AV7" t="n">
         <v>14</v>
@@ -1721,7 +1788,7 @@
         <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" t="n">
         <v>18</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G8" t="n">
-        <v>0.419</v>
+        <v>0.429</v>
       </c>
       <c r="H8" t="n">
         <v>49.2</v>
       </c>
       <c r="I8" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J8" t="n">
-        <v>84.2</v>
+        <v>84</v>
       </c>
       <c r="K8" t="n">
         <v>0.45</v>
@@ -1783,28 +1850,28 @@
         <v>19.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="O8" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P8" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.797</v>
+        <v>0.794</v>
       </c>
       <c r="R8" t="n">
         <v>9.4</v>
       </c>
       <c r="S8" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T8" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U8" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V8" t="n">
         <v>14.5</v>
@@ -1813,10 +1880,10 @@
         <v>7.8</v>
       </c>
       <c r="X8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z8" t="n">
         <v>21.2</v>
@@ -1825,13 +1892,13 @@
         <v>19.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>100.3</v>
+        <v>100.2</v>
       </c>
       <c r="AC8" t="n">
         <v>-2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
         <v>18</v>
@@ -1846,10 +1913,10 @@
         <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK8" t="n">
         <v>12</v>
@@ -1858,10 +1925,10 @@
         <v>14</v>
       </c>
       <c r="AM8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO8" t="n">
         <v>10</v>
@@ -1876,22 +1943,22 @@
         <v>27</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
         <v>18</v>
       </c>
       <c r="AU8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AW8" t="n">
         <v>16</v>
       </c>
       <c r="AX8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY8" t="n">
         <v>8</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>2.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
         <v>6</v>
@@ -2037,7 +2104,7 @@
         <v>5</v>
       </c>
       <c r="AL9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM9" t="n">
         <v>19</v>
@@ -2070,7 +2137,7 @@
         <v>26</v>
       </c>
       <c r="AW9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
@@ -2088,7 +2155,7 @@
         <v>4</v>
       </c>
       <c r="BC9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E10" t="n">
         <v>16</v>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G10" t="n">
-        <v>0.372</v>
+        <v>0.381</v>
       </c>
       <c r="H10" t="n">
         <v>48.6</v>
@@ -2135,19 +2202,19 @@
         <v>36</v>
       </c>
       <c r="J10" t="n">
-        <v>80.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L10" t="n">
         <v>6.3</v>
       </c>
       <c r="M10" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="N10" t="n">
-        <v>0.372</v>
+        <v>0.373</v>
       </c>
       <c r="O10" t="n">
         <v>16.6</v>
@@ -2162,16 +2229,16 @@
         <v>12.6</v>
       </c>
       <c r="S10" t="n">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="T10" t="n">
-        <v>43.5</v>
+        <v>43.7</v>
       </c>
       <c r="U10" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="V10" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W10" t="n">
         <v>6.3</v>
@@ -2186,16 +2253,16 @@
         <v>19.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB10" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.3</v>
+        <v>-0.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
@@ -2207,28 +2274,28 @@
         <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI10" t="n">
         <v>22</v>
       </c>
       <c r="AJ10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK10" t="n">
         <v>15</v>
       </c>
       <c r="AL10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM10" t="n">
         <v>26</v>
       </c>
       <c r="AN10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -2246,7 +2313,7 @@
         <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV10" t="n">
         <v>23</v>
@@ -2261,13 +2328,13 @@
         <v>20</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BC10" t="n">
         <v>17</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -2299,85 +2366,85 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E11" t="n">
         <v>26</v>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>0.619</v>
+        <v>0.634</v>
       </c>
       <c r="H11" t="n">
         <v>48.5</v>
       </c>
       <c r="I11" t="n">
-        <v>37.6</v>
+        <v>37.9</v>
       </c>
       <c r="J11" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K11" t="n">
-        <v>0.455</v>
+        <v>0.457</v>
       </c>
       <c r="L11" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M11" t="n">
         <v>20.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.386</v>
+        <v>0.39</v>
       </c>
       <c r="O11" t="n">
-        <v>17.4</v>
+        <v>17.1</v>
       </c>
       <c r="P11" t="n">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.803</v>
+        <v>0.8</v>
       </c>
       <c r="R11" t="n">
         <v>10.9</v>
       </c>
       <c r="S11" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
       <c r="T11" t="n">
-        <v>44.5</v>
+        <v>44.7</v>
       </c>
       <c r="U11" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="V11" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W11" t="n">
         <v>7</v>
       </c>
       <c r="X11" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>100.4</v>
+        <v>100.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
         <v>6</v>
@@ -2389,16 +2456,16 @@
         <v>7</v>
       </c>
       <c r="AH11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
@@ -2407,10 +2474,10 @@
         <v>12</v>
       </c>
       <c r="AN11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AP11" t="n">
         <v>19</v>
@@ -2428,10 +2495,10 @@
         <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AW11" t="n">
         <v>26</v>
@@ -2443,7 +2510,7 @@
         <v>17</v>
       </c>
       <c r="AZ11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA11" t="n">
         <v>22</v>
@@ -2452,7 +2519,7 @@
         <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F12" t="n">
         <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>0.511</v>
+        <v>0.5</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="J12" t="n">
-        <v>82.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0.453</v>
@@ -2508,10 +2575,10 @@
         <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.356</v>
+        <v>0.353</v>
       </c>
       <c r="O12" t="n">
         <v>19.2</v>
@@ -2520,10 +2587,10 @@
         <v>25.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.754</v>
+        <v>0.753</v>
       </c>
       <c r="R12" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S12" t="n">
         <v>32.1</v>
@@ -2535,34 +2602,34 @@
         <v>22.4</v>
       </c>
       <c r="V12" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="W12" t="n">
         <v>8.6</v>
       </c>
       <c r="X12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="n">
         <v>6.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.1</v>
+        <v>104.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="AD12" t="n">
         <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF12" t="n">
         <v>16</v>
@@ -2574,10 +2641,10 @@
         <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AK12" t="n">
         <v>11</v>
@@ -2589,13 +2656,13 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
         <v>4</v>
       </c>
       <c r="AP12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
         <v>15</v>
@@ -2619,7 +2686,7 @@
         <v>4</v>
       </c>
       <c r="AX12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
@@ -2628,13 +2695,13 @@
         <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BB12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -2741,19 +2808,19 @@
         <v>1.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
         <v>6</v>
       </c>
       <c r="AF13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
         <v>30</v>
@@ -2762,16 +2829,16 @@
         <v>23</v>
       </c>
       <c r="AK13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM13" t="n">
         <v>16</v>
       </c>
       <c r="AN13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
         <v>23</v>
@@ -2780,10 +2847,10 @@
         <v>18</v>
       </c>
       <c r="AQ13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS13" t="n">
         <v>3</v>
@@ -2792,7 +2859,7 @@
         <v>1</v>
       </c>
       <c r="AU13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV13" t="n">
         <v>20</v>
@@ -2810,13 +2877,13 @@
         <v>11</v>
       </c>
       <c r="BA13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC13" t="n">
         <v>10</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>9</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>7.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2941,7 +3008,7 @@
         <v>4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
         <v>4</v>
@@ -2956,7 +3023,7 @@
         <v>17</v>
       </c>
       <c r="AO14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP14" t="n">
         <v>8</v>
@@ -2989,7 +3056,7 @@
         <v>7</v>
       </c>
       <c r="AZ14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -3027,46 +3094,46 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F15" t="n">
         <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>0.419</v>
+        <v>0.405</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J15" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.455</v>
+        <v>0.453</v>
       </c>
       <c r="L15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.356</v>
+        <v>0.354</v>
       </c>
       <c r="O15" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="P15" t="n">
-        <v>27.8</v>
+        <v>28.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.694</v>
+        <v>0.696</v>
       </c>
       <c r="R15" t="n">
         <v>12.3</v>
@@ -3078,7 +3145,7 @@
         <v>44.9</v>
       </c>
       <c r="U15" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V15" t="n">
         <v>15.4</v>
@@ -3087,34 +3154,34 @@
         <v>7.3</v>
       </c>
       <c r="X15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.3</v>
+        <v>102.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH15" t="n">
         <v>29</v>
@@ -3126,16 +3193,16 @@
         <v>20</v>
       </c>
       <c r="AK15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM15" t="n">
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO15" t="n">
         <v>3</v>
@@ -3144,7 +3211,7 @@
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR15" t="n">
         <v>11</v>
@@ -3159,7 +3226,7 @@
         <v>17</v>
       </c>
       <c r="AV15" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AW15" t="n">
         <v>22</v>
@@ -3174,13 +3241,13 @@
         <v>5</v>
       </c>
       <c r="BA15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB15" t="n">
         <v>6</v>
       </c>
       <c r="BC15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -3209,46 +3276,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F16" t="n">
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.667</v>
+        <v>0.659</v>
       </c>
       <c r="H16" t="n">
         <v>48.5</v>
       </c>
       <c r="I16" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="J16" t="n">
-        <v>83</v>
+        <v>82.8</v>
       </c>
       <c r="K16" t="n">
-        <v>0.437</v>
+        <v>0.435</v>
       </c>
       <c r="L16" t="n">
         <v>4.7</v>
       </c>
       <c r="M16" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0.342</v>
+        <v>0.34</v>
       </c>
       <c r="O16" t="n">
-        <v>16.3</v>
+        <v>16.6</v>
       </c>
       <c r="P16" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.788</v>
+        <v>0.792</v>
       </c>
       <c r="R16" t="n">
         <v>13.5</v>
@@ -3260,16 +3327,16 @@
         <v>43</v>
       </c>
       <c r="U16" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V16" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W16" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="X16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y16" t="n">
         <v>6</v>
@@ -3278,16 +3345,16 @@
         <v>19.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3299,37 +3366,37 @@
         <v>5</v>
       </c>
       <c r="AH16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AJ16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AK16" t="n">
         <v>24</v>
       </c>
       <c r="AL16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM16" t="n">
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AQ16" t="n">
         <v>4</v>
       </c>
       <c r="AR16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS16" t="n">
         <v>26</v>
@@ -3338,10 +3405,10 @@
         <v>11</v>
       </c>
       <c r="AU16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW16" t="n">
         <v>2</v>
@@ -3353,13 +3420,13 @@
         <v>23</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BB16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC16" t="n">
         <v>6</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -3391,37 +3458,37 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17" t="n">
         <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J17" t="n">
         <v>78.40000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.491</v>
+        <v>0.489</v>
       </c>
       <c r="L17" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="M17" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.386</v>
+        <v>0.388</v>
       </c>
       <c r="O17" t="n">
         <v>17.4</v>
@@ -3430,16 +3497,16 @@
         <v>22.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.759</v>
+        <v>0.757</v>
       </c>
       <c r="R17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T17" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="U17" t="n">
         <v>22.5</v>
@@ -3448,28 +3515,28 @@
         <v>13.6</v>
       </c>
       <c r="W17" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>102.8</v>
+        <v>102.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
@@ -3481,7 +3548,7 @@
         <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI17" t="n">
         <v>3</v>
@@ -3499,10 +3566,10 @@
         <v>8</v>
       </c>
       <c r="AN17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
@@ -3526,7 +3593,7 @@
         <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX17" t="n">
         <v>18</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -3573,46 +3640,46 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E18" t="n">
         <v>22</v>
       </c>
       <c r="F18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>0.537</v>
+        <v>0.55</v>
       </c>
       <c r="H18" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
       <c r="J18" t="n">
-        <v>86.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="K18" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L18" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="M18" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="N18" t="n">
-        <v>0.345</v>
+        <v>0.339</v>
       </c>
       <c r="O18" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="P18" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.741</v>
+        <v>0.743</v>
       </c>
       <c r="R18" t="n">
         <v>12.7</v>
@@ -3621,19 +3688,19 @@
         <v>30.8</v>
       </c>
       <c r="T18" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U18" t="n">
-        <v>22.2</v>
+        <v>21.9</v>
       </c>
       <c r="V18" t="n">
         <v>14.5</v>
       </c>
       <c r="W18" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X18" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="Y18" t="n">
         <v>4.3</v>
@@ -3642,22 +3709,22 @@
         <v>19.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.3</v>
+        <v>97</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="AD18" t="n">
         <v>26</v>
       </c>
       <c r="AE18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG18" t="n">
         <v>13</v>
@@ -3666,7 +3733,7 @@
         <v>25</v>
       </c>
       <c r="AI18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
@@ -3675,16 +3742,16 @@
         <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AM18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AO18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP18" t="n">
         <v>17</v>
@@ -3696,19 +3763,19 @@
         <v>6</v>
       </c>
       <c r="AS18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AT18" t="n">
         <v>9</v>
       </c>
       <c r="AU18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AV18" t="n">
         <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX18" t="n">
         <v>1</v>
@@ -3723,7 +3790,7 @@
         <v>17</v>
       </c>
       <c r="BB18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC18" t="n">
         <v>16</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -3755,25 +3822,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" t="n">
         <v>17</v>
       </c>
       <c r="F19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G19" t="n">
-        <v>0.425</v>
+        <v>0.436</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="J19" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="K19" t="n">
         <v>0.43</v>
@@ -3782,31 +3849,31 @@
         <v>5.4</v>
       </c>
       <c r="M19" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0.291</v>
+        <v>0.292</v>
       </c>
       <c r="O19" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P19" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.734</v>
+        <v>0.738</v>
       </c>
       <c r="R19" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="S19" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T19" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
       <c r="U19" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V19" t="n">
         <v>15.3</v>
@@ -3815,31 +3882,31 @@
         <v>7.7</v>
       </c>
       <c r="X19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>94.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.1</v>
+        <v>-1.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG19" t="n">
         <v>18</v>
@@ -3848,7 +3915,7 @@
         <v>27</v>
       </c>
       <c r="AI19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ19" t="n">
         <v>18</v>
@@ -3857,7 +3924,7 @@
         <v>26</v>
       </c>
       <c r="AL19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM19" t="n">
         <v>21</v>
@@ -3869,16 +3936,16 @@
         <v>5</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT19" t="n">
         <v>5</v>
@@ -3887,13 +3954,13 @@
         <v>18</v>
       </c>
       <c r="AV19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW19" t="n">
         <v>17</v>
       </c>
       <c r="AX19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY19" t="n">
         <v>22</v>
@@ -3902,13 +3969,13 @@
         <v>2</v>
       </c>
       <c r="BA19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB19" t="n">
         <v>24</v>
       </c>
       <c r="BC19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -3937,28 +4004,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E20" t="n">
         <v>14</v>
       </c>
       <c r="F20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G20" t="n">
-        <v>0.326</v>
+        <v>0.333</v>
       </c>
       <c r="H20" t="n">
         <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J20" t="n">
         <v>80.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L20" t="n">
         <v>7</v>
@@ -3967,7 +4034,7 @@
         <v>18.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.37</v>
+        <v>0.376</v>
       </c>
       <c r="O20" t="n">
         <v>14.4</v>
@@ -3976,22 +4043,22 @@
         <v>18.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.771</v>
+        <v>0.769</v>
       </c>
       <c r="R20" t="n">
         <v>11.5</v>
       </c>
       <c r="S20" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="T20" t="n">
-        <v>41.7</v>
+        <v>41.9</v>
       </c>
       <c r="U20" t="n">
         <v>21.3</v>
       </c>
       <c r="V20" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W20" t="n">
         <v>6.4</v>
@@ -4003,34 +4070,34 @@
         <v>6.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>93.3</v>
+        <v>93.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>-4</v>
+        <v>-3.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE20" t="n">
         <v>26</v>
       </c>
       <c r="AF20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AG20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AJ20" t="n">
         <v>26</v>
@@ -4039,19 +4106,19 @@
         <v>13</v>
       </c>
       <c r="AL20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM20" t="n">
         <v>18</v>
       </c>
       <c r="AN20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO20" t="n">
         <v>27</v>
       </c>
       <c r="AP20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ20" t="n">
         <v>11</v>
@@ -4060,7 +4127,7 @@
         <v>16</v>
       </c>
       <c r="AS20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT20" t="n">
         <v>19</v>
@@ -4075,10 +4142,10 @@
         <v>28</v>
       </c>
       <c r="AX20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ20" t="n">
         <v>18</v>
@@ -4087,10 +4154,10 @@
         <v>26</v>
       </c>
       <c r="BB20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>4.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE21" t="n">
         <v>6</v>
@@ -4209,7 +4276,7 @@
         <v>6</v>
       </c>
       <c r="AH21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI21" t="n">
         <v>15</v>
@@ -4242,13 +4309,13 @@
         <v>21</v>
       </c>
       <c r="AS21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E22" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F22" t="n">
         <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>0.773</v>
+        <v>0.767</v>
       </c>
       <c r="H22" t="n">
         <v>48.6</v>
@@ -4319,22 +4386,22 @@
         <v>37.7</v>
       </c>
       <c r="J22" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0.478</v>
       </c>
       <c r="L22" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M22" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.388</v>
+        <v>0.391</v>
       </c>
       <c r="O22" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="P22" t="n">
         <v>27.3</v>
@@ -4346,22 +4413,22 @@
         <v>10.6</v>
       </c>
       <c r="S22" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T22" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U22" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V22" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="W22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="Y22" t="n">
         <v>4.1</v>
@@ -4370,16 +4437,16 @@
         <v>20.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB22" t="n">
         <v>105.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,10 +4458,10 @@
         <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ22" t="n">
         <v>29</v>
@@ -4403,10 +4470,10 @@
         <v>3</v>
       </c>
       <c r="AL22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN22" t="n">
         <v>1</v>
@@ -4424,7 +4491,7 @@
         <v>24</v>
       </c>
       <c r="AS22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -4561,13 +4628,13 @@
         <v>-3.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
       </c>
       <c r="AF23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG23" t="n">
         <v>26</v>
@@ -4576,13 +4643,13 @@
         <v>18</v>
       </c>
       <c r="AI23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL23" t="n">
         <v>16</v>
@@ -4591,7 +4658,7 @@
         <v>17</v>
       </c>
       <c r="AN23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4609,7 +4676,7 @@
         <v>8</v>
       </c>
       <c r="AT23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU23" t="n">
         <v>5</v>
@@ -4624,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="AY23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ23" t="n">
         <v>10</v>
@@ -4633,7 +4700,7 @@
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC23" t="n">
         <v>23</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -4743,37 +4810,37 @@
         <v>-4.2</v>
       </c>
       <c r="AD24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE24" t="n">
         <v>19</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AF24" t="n">
         <v>20</v>
       </c>
-      <c r="AF24" t="n">
-        <v>19</v>
-      </c>
       <c r="AG24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH24" t="n">
         <v>18</v>
       </c>
       <c r="AI24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="n">
         <v>20</v>
       </c>
       <c r="AM24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4794,7 +4861,7 @@
         <v>22</v>
       </c>
       <c r="AU24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV24" t="n">
         <v>3</v>
@@ -4809,7 +4876,7 @@
         <v>9</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA24" t="n">
         <v>29</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -4925,22 +4992,22 @@
         <v>-3.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>25</v>
       </c>
       <c r="AF25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG25" t="n">
         <v>25</v>
       </c>
       <c r="AH25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ25" t="n">
         <v>4</v>
@@ -4952,7 +5019,7 @@
         <v>25</v>
       </c>
       <c r="AM25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN25" t="n">
         <v>29</v>
@@ -4967,7 +5034,7 @@
         <v>20</v>
       </c>
       <c r="AR25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS25" t="n">
         <v>27</v>
@@ -4976,7 +5043,7 @@
         <v>27</v>
       </c>
       <c r="AU25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV25" t="n">
         <v>5</v>
@@ -5000,7 +5067,7 @@
         <v>18</v>
       </c>
       <c r="BC25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-1.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
         <v>16</v>
@@ -5116,10 +5183,10 @@
         <v>15</v>
       </c>
       <c r="AG26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI26" t="n">
         <v>20</v>
@@ -5140,7 +5207,7 @@
         <v>26</v>
       </c>
       <c r="AO26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
         <v>21</v>
@@ -5155,13 +5222,13 @@
         <v>18</v>
       </c>
       <c r="AT26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU26" t="n">
         <v>22</v>
       </c>
       <c r="AV26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW26" t="n">
         <v>20</v>
@@ -5179,7 +5246,7 @@
         <v>24</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC26" t="n">
         <v>19</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E27" t="n">
         <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G27" t="n">
-        <v>0.364</v>
+        <v>0.372</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
@@ -5232,28 +5299,28 @@
         <v>83.2</v>
       </c>
       <c r="K27" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L27" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M27" t="n">
         <v>18.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.356</v>
+        <v>0.353</v>
       </c>
       <c r="O27" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P27" t="n">
         <v>22.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="R27" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S27" t="n">
         <v>28.6</v>
@@ -5262,13 +5329,13 @@
         <v>40.7</v>
       </c>
       <c r="U27" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="V27" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W27" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X27" t="n">
         <v>4.7</v>
@@ -5277,58 +5344,58 @@
         <v>6.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AA27" t="n">
         <v>19.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6</v>
+        <v>-5.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>22</v>
       </c>
       <c r="AF27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI27" t="n">
         <v>17</v>
       </c>
       <c r="AJ27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK27" t="n">
         <v>21</v>
       </c>
       <c r="AL27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM27" t="n">
         <v>20</v>
       </c>
       <c r="AN27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP27" t="n">
         <v>13</v>
       </c>
       <c r="AQ27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR27" t="n">
         <v>12</v>
@@ -5337,19 +5404,19 @@
         <v>29</v>
       </c>
       <c r="AT27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU27" t="n">
         <v>26</v>
       </c>
       <c r="AV27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW27" t="n">
         <v>14</v>
       </c>
       <c r="AX27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY27" t="n">
         <v>27</v>
@@ -5361,7 +5428,7 @@
         <v>16</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -5393,25 +5460,25 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F28" t="n">
         <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>0.761</v>
+        <v>0.756</v>
       </c>
       <c r="H28" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I28" t="n">
         <v>39.7</v>
       </c>
       <c r="J28" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K28" t="n">
         <v>0.486</v>
@@ -5429,31 +5496,31 @@
         <v>16.2</v>
       </c>
       <c r="P28" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.784</v>
+        <v>0.785</v>
       </c>
       <c r="R28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="T28" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U28" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="V28" t="n">
         <v>15</v>
       </c>
       <c r="W28" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y28" t="n">
         <v>4.8</v>
@@ -5462,10 +5529,10 @@
         <v>17.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.3</v>
+        <v>104.1</v>
       </c>
       <c r="AC28" t="n">
         <v>8.1</v>
@@ -5483,7 +5550,7 @@
         <v>2</v>
       </c>
       <c r="AH28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5501,13 +5568,13 @@
         <v>6</v>
       </c>
       <c r="AN28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO28" t="n">
         <v>21</v>
       </c>
       <c r="AP28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ28" t="n">
         <v>6</v>
@@ -5528,13 +5595,13 @@
         <v>21</v>
       </c>
       <c r="AW28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX28" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AY28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5543,7 +5610,7 @@
         <v>28</v>
       </c>
       <c r="BB28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -5653,22 +5720,22 @@
         <v>-1.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
         <v>22</v>
       </c>
       <c r="AF29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH29" t="n">
         <v>2</v>
       </c>
       <c r="AI29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ29" t="n">
         <v>15</v>
@@ -5677,13 +5744,13 @@
         <v>16</v>
       </c>
       <c r="AL29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM29" t="n">
         <v>7</v>
       </c>
       <c r="AN29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO29" t="n">
         <v>15</v>
@@ -5704,13 +5771,13 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX29" t="n">
         <v>24</v>
@@ -5722,13 +5789,13 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB29" t="n">
         <v>12</v>
       </c>
       <c r="BC29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -5757,19 +5824,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E30" t="n">
         <v>23</v>
       </c>
       <c r="F30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G30" t="n">
-        <v>0.535</v>
+        <v>0.548</v>
       </c>
       <c r="H30" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I30" t="n">
         <v>36.7</v>
@@ -5778,43 +5845,43 @@
         <v>82</v>
       </c>
       <c r="K30" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L30" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M30" t="n">
         <v>17.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0.368</v>
+        <v>0.371</v>
       </c>
       <c r="O30" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="P30" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R30" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S30" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="T30" t="n">
-        <v>42.3</v>
+        <v>42.6</v>
       </c>
       <c r="U30" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="V30" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W30" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X30" t="n">
         <v>6.3</v>
@@ -5823,19 +5890,19 @@
         <v>6.1</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.2</v>
+        <v>98.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
         <v>13</v>
@@ -5847,10 +5914,10 @@
         <v>14</v>
       </c>
       <c r="AH30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ30" t="n">
         <v>17</v>
@@ -5874,37 +5941,37 @@
         <v>9</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW30" t="n">
         <v>10</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>8</v>
       </c>
       <c r="AX30" t="n">
         <v>6</v>
       </c>
       <c r="AY30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ30" t="n">
         <v>28</v>
       </c>
       <c r="BA30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB30" t="n">
         <v>11</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
@@ -5939,58 +6006,58 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F31" t="n">
         <v>31</v>
       </c>
       <c r="G31" t="n">
-        <v>0.244</v>
+        <v>0.225</v>
       </c>
       <c r="H31" t="n">
         <v>48.9</v>
       </c>
       <c r="I31" t="n">
-        <v>35</v>
+        <v>34.7</v>
       </c>
       <c r="J31" t="n">
         <v>83.2</v>
       </c>
       <c r="K31" t="n">
-        <v>0.421</v>
+        <v>0.417</v>
       </c>
       <c r="L31" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M31" t="n">
         <v>19.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.342</v>
+        <v>0.339</v>
       </c>
       <c r="O31" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="P31" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.733</v>
+        <v>0.736</v>
       </c>
       <c r="R31" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="S31" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T31" t="n">
-        <v>43.7</v>
+        <v>43.9</v>
       </c>
       <c r="U31" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V31" t="n">
         <v>15.4</v>
@@ -5999,43 +6066,43 @@
         <v>7.5</v>
       </c>
       <c r="X31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y31" t="n">
         <v>5</v>
       </c>
-      <c r="Y31" t="n">
-        <v>4.9</v>
-      </c>
       <c r="Z31" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA31" t="n">
         <v>19.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>91.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-5.3</v>
+        <v>-5.8</v>
       </c>
       <c r="AD31" t="n">
         <v>26</v>
       </c>
       <c r="AE31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF31" t="n">
         <v>28</v>
       </c>
       <c r="AG31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI31" t="n">
         <v>29</v>
       </c>
-      <c r="AH31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>28</v>
-      </c>
       <c r="AJ31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK31" t="n">
         <v>30</v>
@@ -6047,7 +6114,7 @@
         <v>15</v>
       </c>
       <c r="AN31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO31" t="n">
         <v>25</v>
@@ -6059,13 +6126,13 @@
         <v>24</v>
       </c>
       <c r="AR31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU31" t="n">
         <v>20</v>
@@ -6077,19 +6144,19 @@
         <v>18</v>
       </c>
       <c r="AX31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA31" t="n">
         <v>23</v>
       </c>
       <c r="BB31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-25-2012-13</t>
+          <t>2013-01-25</t>
         </is>
       </c>
     </row>
